--- a/branches/examples-naming-and-ratio/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/examples-naming-and-ratio/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.rc4</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:41:11+00:00</t>
+    <t>2026-09-08T11:49:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
